--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H610"/>
+  <dimension ref="A1:H611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16298,6 +16298,32 @@
       </c>
       <c r="H610" t="n">
         <v>7.74</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B611" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="C611" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D611" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="E611" t="n">
+        <v>54</v>
+      </c>
+      <c r="F611" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="G611" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H611" t="n">
+        <v>8.15</v>
       </c>
     </row>
   </sheetData>
@@ -16311,7 +16337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K610"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37684,6 +37710,41 @@
       </c>
       <c r="K610" t="n">
         <v>2.75</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B611" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="C611" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D611" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="E611" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="F611" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="G611" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="H611" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I611" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J611" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K611" t="n">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H611"/>
+  <dimension ref="A1:H612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16336,6 +16336,32 @@
       </c>
       <c r="H611" t="n">
         <v>8.15</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B612" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="C612" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="D612" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="E612" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="F612" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="G612" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="H612" t="n">
+        <v>8.050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16349,7 +16375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K611"/>
+  <dimension ref="A1:K612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37757,6 +37783,41 @@
       </c>
       <c r="K611" t="n">
         <v>2.8</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B612" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="C612" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="D612" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="E612" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="F612" t="n">
+        <v>38</v>
+      </c>
+      <c r="G612" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="H612" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I612" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J612" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K612" t="n">
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H613"/>
+  <dimension ref="A1:H614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16376,6 +16376,32 @@
       </c>
       <c r="H613" t="n">
         <v>7.93</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B614" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="C614" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="D614" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="E614" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="F614" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="G614" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="H614" t="n">
+        <v>8.41</v>
       </c>
     </row>
   </sheetData>
@@ -16389,7 +16415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K613"/>
+  <dimension ref="A1:K614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37867,6 +37893,41 @@
       </c>
       <c r="K613" t="n">
         <v>2.75</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B614" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="C614" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="D614" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="E614" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="F614" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="G614" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="H614" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I614" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J614" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K614" t="n">
+        <v>2.73</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H615"/>
+  <dimension ref="A1:H616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16428,6 +16428,32 @@
       </c>
       <c r="H615" t="n">
         <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B616" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="C616" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D616" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E616" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="F616" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="G616" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="H616" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -16441,7 +16467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K615"/>
+  <dimension ref="A1:K616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37989,6 +38015,41 @@
       </c>
       <c r="K615" t="n">
         <v>2.93</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B616" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="C616" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D616" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="E616" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F616" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="G616" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="H616" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I616" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J616" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="K616" t="n">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H616"/>
+  <dimension ref="A1:H617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16454,6 +16454,32 @@
       </c>
       <c r="H616" t="n">
         <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B617" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C617" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="D617" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E617" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="F617" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="G617" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H617" t="n">
+        <v>8.140000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16467,7 +16493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K616"/>
+  <dimension ref="A1:K617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38050,6 +38076,41 @@
       </c>
       <c r="K616" t="n">
         <v>2.8</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B617" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="C617" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="D617" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="E617" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="F617" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="G617" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="H617" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I617" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J617" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K617" t="n">
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
